--- a/erp-server/erp-server-tms/src/main/resources/excel/declareReconciliationDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/declareReconciliationDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <r>
       <t>*</t>
@@ -59,6 +59,21 @@
   </si>
   <si>
     <t>重量单位</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>币种</t>
+    </r>
   </si>
   <si>
     <t>kg</t>
@@ -1002,8 +1017,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="10.875" customWidth="1"/>
@@ -1011,7 +1026,7 @@
     <col min="5" max="5" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1030,10 +1045,13 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="6:6">
       <c r="F2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
